--- a/processo_2/synthetic_proposals/PROPOSTA_009/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_009/ficha_pontuacao.xlsx
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -799,33 +799,17 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7141-5496</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -966,7 +950,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -989,7 +973,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1083,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,7 +1110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1149,7 +1133,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1195,7 +1179,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1241,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1264,17 +1248,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1287,17 +1271,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1310,7 +1294,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1333,7 +1317,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1423,13 +1407,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr"/>
     </row>
@@ -1551,7 +1535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1620,7 +1604,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1643,7 +1627,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1807,13 +1791,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr"/>
     </row>
@@ -1851,7 +1835,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1866,7 +1850,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
